--- a/plantillas/53.xlsx
+++ b/plantillas/53.xlsx
@@ -10510,7 +10510,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>19.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/53.xlsx
+++ b/plantillas/53.xlsx
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>21.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/53.xlsx
+++ b/plantillas/53.xlsx
@@ -9552,7 +9552,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>23.10.2026</t>
         </is>
       </c>
     </row>
